--- a/app/Imports/excel-importation/2025-db-import -prod -2 - rabat.xlsx
+++ b/app/Imports/excel-importation/2025-db-import -prod -2 - rabat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Developpement 2025\grace_back_prod\app\Imports\excel-importation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4002AE6-A70C-4D96-A12D-E88488B4C5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02FC7DB-1B9F-4009-B283-1976D49CAFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="106">
   <si>
     <t>user_id</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>32009/2025</t>
+  </si>
+  <si>
+    <t>adresse</t>
   </si>
 </sst>
 </file>
@@ -424,7 +427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -438,6 +441,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -718,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="7" bestFit="1" customWidth="1"/>
@@ -740,9 +744,10 @@
     <col min="22" max="22" width="25.7109375" customWidth="1"/>
     <col min="23" max="23" width="13.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -816,10 +821,13 @@
         <v>22</v>
       </c>
       <c r="Y1" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z1" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>5</v>
       </c>
@@ -890,11 +898,12 @@
       <c r="X2" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="7"/>
+      <c r="Z2">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>5</v>
       </c>
@@ -965,11 +974,12 @@
       <c r="X3" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="7"/>
+      <c r="Z3">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>5</v>
       </c>
@@ -1040,11 +1050,12 @@
       <c r="X4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="7"/>
+      <c r="Z4">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>5</v>
       </c>
@@ -1115,11 +1126,12 @@
       <c r="X5" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="7"/>
+      <c r="Z5">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1190,11 +1202,12 @@
       <c r="X6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="7"/>
+      <c r="Z6">
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1265,11 +1278,12 @@
       <c r="X7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="7"/>
+      <c r="Z7">
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -1334,11 +1348,12 @@
       <c r="X8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="7"/>
+      <c r="Z8">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -1403,7 +1418,8 @@
       <c r="X9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="7"/>
+      <c r="Z9">
         <v>99</v>
       </c>
     </row>
